--- a/docs/Calculations.xlsx
+++ b/docs/Calculations.xlsx
@@ -4,21 +4,22 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Активное" sheetId="1" r:id="rId1"/>
     <sheet name="Пассивное" sheetId="2" r:id="rId2"/>
-    <sheet name="ПО" sheetId="3" r:id="rId3"/>
+    <sheet name="ПО(-)" sheetId="3" r:id="rId3"/>
     <sheet name="Оплата труда" sheetId="4" r:id="rId4"/>
-    <sheet name="Сметная стоимость" sheetId="5" r:id="rId5"/>
+    <sheet name="Смета работ" sheetId="6" r:id="rId5"/>
+    <sheet name="ИТОГО" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="70">
   <si>
     <t>№</t>
   </si>
@@ -113,54 +114,12 @@
     <t>Оплата труда администратора (0,5 ставки)</t>
   </si>
   <si>
-    <t>Тип оборудования</t>
-  </si>
-  <si>
-    <t>417 091</t>
-  </si>
-  <si>
-    <t>19 300</t>
-  </si>
-  <si>
-    <t>Итого оборудование</t>
-  </si>
-  <si>
-    <t>436 391</t>
-  </si>
-  <si>
     <t>Активное оборудование</t>
   </si>
   <si>
     <t>Пассивное оборудование</t>
   </si>
   <si>
-    <t>28 560</t>
-  </si>
-  <si>
-    <t>32 160</t>
-  </si>
-  <si>
-    <t>32 700</t>
-  </si>
-  <si>
-    <t>Итого оплата труда</t>
-  </si>
-  <si>
-    <t>93 420</t>
-  </si>
-  <si>
-    <t>Страховые взносы (30,2%)</t>
-  </si>
-  <si>
-    <t>28 213</t>
-  </si>
-  <si>
-    <t>Расчёт затрат на оплату труда и страховых взносов</t>
-  </si>
-  <si>
-    <t>Расчёт затрат на оборудование</t>
-  </si>
-  <si>
     <t>Статья затрат</t>
   </si>
   <si>
@@ -170,67 +129,18 @@
     <t>Амортизация оборудования</t>
   </si>
   <si>
-    <t>436 391 / 36 мес. × 12 мес.</t>
-  </si>
-  <si>
     <t>Затраты на электроэнергию</t>
   </si>
   <si>
-    <t>0,213 кВт × 24 ч × 365 дн × 7 руб.</t>
-  </si>
-  <si>
-    <t>25 000 руб./мес. × 12 мес.</t>
-  </si>
-  <si>
     <t>Страховые взносы на администратора</t>
   </si>
   <si>
-    <t>300 000 × 0,302</t>
-  </si>
-  <si>
-    <t>Итого годовые эксплуатационные затраты</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Расчёт годовых эксплуатационных затрат
-</t>
-  </si>
-  <si>
-    <t>Сводная смета затрат</t>
-  </si>
-  <si>
-    <t>Оборудование (активное и пассивное)</t>
-  </si>
-  <si>
-    <t>Лицензионное программное обеспечение</t>
-  </si>
-  <si>
-    <t>433 500</t>
-  </si>
-  <si>
     <t>Оплата труда работников</t>
   </si>
   <si>
     <t>Страховые взносы</t>
   </si>
   <si>
-    <t>Итого единовременные затраты</t>
-  </si>
-  <si>
-    <t>991 524</t>
-  </si>
-  <si>
-    <t>Годовые эксплуатационные затраты</t>
-  </si>
-  <si>
-    <t>549 125</t>
-  </si>
-  <si>
-    <t>Всего за первый год</t>
-  </si>
-  <si>
-    <t>1 540 649</t>
-  </si>
-  <si>
     <t>Итого:</t>
   </si>
   <si>
@@ -240,9 +150,6 @@
     <t>Astra Linux Special Edition</t>
   </si>
   <si>
-    <t>21 675</t>
-  </si>
-  <si>
     <t>Модель / Характеристики</t>
   </si>
   <si>
@@ -283,13 +190,62 @@
   </si>
   <si>
     <t>Часовая ставка, руб.</t>
+  </si>
+  <si>
+    <t>Категория</t>
+  </si>
+  <si>
+    <t>Итого</t>
+  </si>
+  <si>
+    <t>Цена</t>
+  </si>
+  <si>
+    <t>Сумма</t>
+  </si>
+  <si>
+    <t>Разработка проекта</t>
+  </si>
+  <si>
+    <t>Ставка страх. Взносов</t>
+  </si>
+  <si>
+    <t>Час. ставка, руб.</t>
+  </si>
+  <si>
+    <t>Оборудование и материалы</t>
+  </si>
+  <si>
+    <t>Оборудование</t>
+  </si>
+  <si>
+    <t>Сводная смета стоимости работ (единовременные затраты)</t>
+  </si>
+  <si>
+    <t>Затраты на оплату труда работников</t>
+  </si>
+  <si>
+    <t>Трудоёмкость и стоимость оплаты труда работников:</t>
+  </si>
+  <si>
+    <t>Годовые эксплуатационные затраты (после ввода сети в эксплуатацию)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="171" formatCode="_-* #,##0.00\ [$₽-419]_-;\-* #,##0.00\ [$₽-419]_-;_-* &quot;-&quot;??\ [$₽-419]_-;_-@_-"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -301,10 +257,24 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -324,24 +294,51 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Процентный" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -643,123 +640,234 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.140625" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2">
+        <v>4</v>
+      </c>
+      <c r="E2" s="3">
+        <v>71205</v>
+      </c>
+      <c r="F2" s="3">
+        <f>D2*E2</f>
+        <v>284820</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3">
+        <v>66791</v>
+      </c>
+      <c r="F3" s="3">
+        <f t="shared" ref="F3:F6" si="0">D3*E3</f>
+        <v>66791</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2">
+      <c r="E4" s="3">
+        <v>52000</v>
+      </c>
+      <c r="F4" s="3">
+        <f t="shared" si="0"/>
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="E2">
-        <v>71205</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3">
+      <c r="B5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="2">
         <v>1</v>
       </c>
-      <c r="E3">
-        <v>66791</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4">
+      <c r="E5" s="3">
+        <v>7490</v>
+      </c>
+      <c r="F5" s="3">
+        <f t="shared" si="0"/>
+        <v>7490</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="2">
         <v>1</v>
       </c>
-      <c r="E4">
-        <v>52000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>7490</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
+      <c r="E6" s="3">
         <v>5990</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>70</v>
+      <c r="F6" s="3">
+        <f t="shared" si="0"/>
+        <v>5990</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="B17" s="3">
-        <f>SUM(E2:E6)</f>
-        <v>203476</v>
-      </c>
+        <f>SUM(F2:F6)</f>
+        <v>417091</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -770,44 +878,54 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D2">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="E2">
+      <c r="B2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3">
         <v>4850</v>
       </c>
       <c r="F2" s="4">
@@ -816,19 +934,19 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D3">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="2">
         <v>25</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="3">
         <v>180</v>
       </c>
       <c r="F3" s="4">
@@ -837,19 +955,19 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D4">
+      <c r="C4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="2">
         <v>10</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="3">
         <v>150</v>
       </c>
       <c r="F4" s="4">
@@ -858,19 +976,19 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D5">
+      <c r="C5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="2">
         <v>5</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="3">
         <v>250</v>
       </c>
       <c r="F5" s="4">
@@ -879,19 +997,19 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D6">
+      <c r="C6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="2">
         <v>2</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="3">
         <v>2100</v>
       </c>
       <c r="F6" s="4">
@@ -900,19 +1018,19 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D7">
+      <c r="C7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="2">
         <v>1</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="3">
         <v>500</v>
       </c>
       <c r="F7" s="4">
@@ -921,19 +1039,19 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>1</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="3">
         <v>300</v>
       </c>
       <c r="F8" s="4">
@@ -942,19 +1060,19 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>13</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="2">
         <v>1</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="3">
         <v>200</v>
       </c>
       <c r="F9" s="4">
@@ -963,19 +1081,19 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C10" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10">
+      <c r="C10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="2">
         <v>4</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="3">
         <v>500</v>
       </c>
       <c r="F10" s="4">
@@ -984,10 +1102,10 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>70</v>
-      </c>
-      <c r="B17">
+      <c r="A17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="13">
         <f>SUM(F2:F10)</f>
         <v>19300</v>
       </c>
@@ -1002,44 +1120,50 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="2"/>
+    <col min="2" max="2" width="24.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C2">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E2" t="s">
-        <v>61</v>
+      <c r="B2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2" s="3">
+        <v>21675</v>
+      </c>
+      <c r="E2" s="3">
+        <f>C2*D2</f>
+        <v>65025</v>
       </c>
     </row>
   </sheetData>
@@ -1049,358 +1173,402 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.5703125" customWidth="1"/>
-    <col min="2" max="2" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="D2" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C2">
+      <c r="C3" s="2">
         <v>80</v>
       </c>
-      <c r="D2">
+      <c r="D3" s="3">
         <v>357</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C3">
+      <c r="C4" s="2">
         <v>120</v>
       </c>
-      <c r="D3">
+      <c r="D4" s="3">
         <v>268</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C4">
+      <c r="C5" s="2">
         <v>100</v>
       </c>
-      <c r="D4">
+      <c r="D5" s="3">
         <v>327</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B1" s="2"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="1" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="2">
+        <f>'Оплата труда'!C3</f>
+        <v>80</v>
+      </c>
+      <c r="C3" s="3">
+        <f>'Оплата труда'!D3</f>
+        <v>357</v>
+      </c>
+      <c r="D3" s="3">
+        <f>B3*C3</f>
+        <v>28560</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="2">
+        <f>'Оплата труда'!C4</f>
+        <v>120</v>
+      </c>
+      <c r="C4" s="3">
+        <f>'Оплата труда'!D4</f>
+        <v>268</v>
+      </c>
+      <c r="D4" s="3">
+        <f t="shared" ref="D4:D5" si="0">B4*C4</f>
+        <v>32160</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="2">
+        <f>'Оплата труда'!C5</f>
+        <v>100</v>
+      </c>
+      <c r="C5" s="3">
+        <f>'Оплата труда'!D5</f>
+        <v>327</v>
+      </c>
+      <c r="D5" s="3">
+        <f t="shared" si="0"/>
+        <v>32700</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="3">
+        <f>SUM(D3:D5)</f>
+        <v>93420</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="7"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="3">
+        <f>D6</f>
+        <v>93420</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="8">
+        <v>0.30199999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="3">
+        <f>B9*B10</f>
+        <v>28212.84</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A8:B8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="40.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" style="2" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="6"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" s="3">
+        <f>Активное!B17</f>
+        <v>417091</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="3">
+        <f>Пассивное!B17</f>
+        <v>19300</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="13">
+        <f>SUM(B3:B4)</f>
+        <v>436391</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="6"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="12">
+        <f>B5</f>
+        <v>436391</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="3">
+        <f>'Смета работ'!D6</f>
+        <v>93420</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="3">
+        <f>'Смета работ'!B11</f>
+        <v>28212.84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="13">
+        <f>SUM(B9:B11)</f>
+        <v>558023.84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="3">
+        <f>B5/36*12</f>
+        <v>145463.66666666669</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B17" s="3">
+        <f>0.213*24*365*7</f>
+        <v>13061.16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="3">
+        <f>25000*12</f>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="1"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="B19" s="3">
+        <f>300000*'Смета работ'!B10</f>
+        <v>90600</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" s="1"/>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" t="s">
-        <v>44</v>
+      <c r="B20" s="13">
+        <f>SUM(B16:B19)</f>
+        <v>549124.82666666666</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B23" s="1"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>51</v>
-      </c>
-      <c r="B26" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>56</v>
-      </c>
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B31" s="1"/>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>47</v>
-      </c>
-      <c r="B32" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>59</v>
-      </c>
-      <c r="B33" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>60</v>
-      </c>
-      <c r="B34" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>62</v>
-      </c>
-      <c r="B35" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>63</v>
-      </c>
-      <c r="B36" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>64</v>
-      </c>
-      <c r="B37" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>66</v>
-      </c>
-      <c r="B38" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>68</v>
-      </c>
-      <c r="B39" t="s">
-        <v>69</v>
-      </c>
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A15:B15"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>